--- a/data/trans_orig/P33_1_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33107</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>11445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27959</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>30757</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57019</t>
+          <t>56755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90137</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91975</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131300</t>
+          <t>132326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158367</t>
+          <t>160133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210508</t>
+          <t>208657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>570792</t>
+          <t>571241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>607146</t>
+          <t>607511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>534181</t>
+          <t>533258</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>574884</t>
+          <t>575390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1117298</t>
+          <t>1116085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1171282</t>
+          <t>1172147</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47669</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80550</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>45609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76493</t>
+          <t>74799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115784</t>
+          <t>116848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114377</t>
+          <t>113213</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>157450</t>
+          <t>158929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175854</t>
+          <t>173753</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>226824</t>
+          <t>225587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>302547</t>
+          <t>301775</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>370941</t>
+          <t>373206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>721235</t>
+          <t>726930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>775614</t>
+          <t>778976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>703724</t>
+          <t>701946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>757744</t>
+          <t>757605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1444050</t>
+          <t>1439701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1521934</t>
+          <t>1518491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15395</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35381</t>
+          <t>36096</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>66861</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93148</t>
+          <t>92301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>131057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153999</t>
+          <t>154360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200088</t>
+          <t>200021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>258186</t>
+          <t>259759</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318572</t>
+          <t>318390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>515933</t>
+          <t>512903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556852</t>
+          <t>556284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447687</t>
+          <t>448351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494765</t>
+          <t>496263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>977099</t>
+          <t>978458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1041495</t>
+          <t>1040524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23132</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42595</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69597</t>
+          <t>69388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68532</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103956</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118272</t>
+          <t>119933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161216</t>
+          <t>164640</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163817</t>
+          <t>163768</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214151</t>
+          <t>215396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297027</t>
+          <t>295537</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363012</t>
+          <t>359898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>729422</t>
+          <t>725693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>775001</t>
+          <t>773764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>765049</t>
+          <t>763987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>817914</t>
+          <t>818790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1505025</t>
+          <t>1508754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1578705</t>
+          <t>1578864</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119005</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165359</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>153480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238714</t>
+          <t>238600</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>417884</t>
+          <t>419514</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>498886</t>
+          <t>500762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>628010</t>
+          <t>630708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>723669</t>
+          <t>722399</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1074562</t>
+          <t>1073329</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1195232</t>
+          <t>1192458</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>51859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>39573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51341</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84169</t>
+          <t>84709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135769</t>
+          <t>135281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179068</t>
+          <t>180994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178392</t>
+          <t>179710</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226039</t>
+          <t>226508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>326001</t>
+          <t>327858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393635</t>
+          <t>396628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>483210</t>
+          <t>481461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>529832</t>
+          <t>529482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>438934</t>
+          <t>441247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>489769</t>
+          <t>490721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>936928</t>
+          <t>934431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1008169</t>
+          <t>1006297</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48466</t>
+          <t>49291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80646</t>
+          <t>81153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54070</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87396</t>
+          <t>85327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111799</t>
+          <t>110670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157172</t>
+          <t>158913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>179485</t>
+          <t>178220</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233312</t>
+          <t>230213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254089</t>
+          <t>251767</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313061</t>
+          <t>311824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445470</t>
+          <t>448977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>527122</t>
+          <t>529155</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>718364</t>
+          <t>719667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>777590</t>
+          <t>775604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>647054</t>
+          <t>649722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>707700</t>
+          <t>712514</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1384325</t>
+          <t>1380295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1471986</t>
+          <t>1469136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47224</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>52264</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>88486</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115254</t>
+          <t>113668</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160092</t>
+          <t>160762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171466</t>
+          <t>169592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>221578</t>
+          <t>218856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296077</t>
+          <t>298831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364467</t>
+          <t>366571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561382</t>
+          <t>557764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609637</t>
+          <t>608382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520865</t>
+          <t>522266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>572091</t>
+          <t>573827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1097217</t>
+          <t>1097831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168881</t>
+          <t>1168645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>43648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75983</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66502</t>
+          <t>66341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>88589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130647</t>
+          <t>129398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169905</t>
+          <t>168339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221082</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>261987</t>
+          <t>260329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319114</t>
+          <t>319247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>447647</t>
+          <t>446227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>527371</t>
+          <t>523967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>656713</t>
+          <t>657622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>714323</t>
+          <t>713454</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>671691</t>
+          <t>672749</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>731714</t>
+          <t>733412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1345434</t>
+          <t>1348374</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1429197</t>
+          <t>1432030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164222</t>
+          <t>166372</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224925</t>
+          <t>224016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154361</t>
+          <t>154515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208100</t>
+          <t>208287</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418265</t>
+          <t>412757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645503</t>
+          <t>642439</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>742186</t>
+          <t>740652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>916489</t>
+          <t>915501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1027372</t>
+          <t>1034270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1588926</t>
+          <t>1588104</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1735899</t>
+          <t>1742073</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2477335</t>
+          <t>2471615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2580460</t>
+          <t>2581173</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2340558</t>
+          <t>2329295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2457196</t>
+          <t>2449801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4842118</t>
+          <t>4851463</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5001553</t>
+          <t>5009745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31451</t>
+          <t>31078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57515</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32612</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>59287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71297</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120910</t>
+          <t>120929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139854</t>
+          <t>140095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183478</t>
+          <t>184955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228950</t>
+          <t>232246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289831</t>
+          <t>293227</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505405</t>
+          <t>507067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>549939</t>
+          <t>550679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>432859</t>
+          <t>433208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481653</t>
+          <t>481863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>955580</t>
+          <t>952749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1020602</t>
+          <t>1017561</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>21788</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>43166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22949</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>48358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48915</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80101</t>
+          <t>84250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140951</t>
+          <t>144657</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>190265</t>
+          <t>193657</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223096</t>
+          <t>221870</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281238</t>
+          <t>277847</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>382270</t>
+          <t>376935</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>458166</t>
+          <t>453075</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>796122</t>
+          <t>792646</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>847798</t>
+          <t>845302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>724329</t>
+          <t>725997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>786472</t>
+          <t>786637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1541014</t>
+          <t>1537052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1617629</t>
+          <t>1615510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>36259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63325</t>
+          <t>63984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49962</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67817</t>
+          <t>67238</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103592</t>
+          <t>105350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130017</t>
+          <t>129290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174481</t>
+          <t>174192</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>181234</t>
+          <t>180552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232693</t>
+          <t>230616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324380</t>
+          <t>320819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389196</t>
+          <t>386975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>534380</t>
+          <t>534531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>587830</t>
+          <t>585550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515456</t>
+          <t>517904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>567935</t>
+          <t>569613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1069362</t>
+          <t>1068561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1140442</t>
+          <t>1140714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48238</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76568</t>
+          <t>78672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35865</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65228</t>
+          <t>64593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93230</t>
+          <t>91586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133953</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159973</t>
+          <t>161098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209857</t>
+          <t>211256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200323</t>
+          <t>202082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254867</t>
+          <t>254456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378739</t>
+          <t>379327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>450564</t>
+          <t>448967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>663580</t>
+          <t>662974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>715942</t>
+          <t>716948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>735752</t>
+          <t>731606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>795557</t>
+          <t>791465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1411995</t>
+          <t>1414247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1492077</t>
+          <t>1491979</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158712</t>
+          <t>159493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211330</t>
+          <t>214797</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139413</t>
+          <t>136422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191263</t>
+          <t>188581</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308090</t>
+          <t>309390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>381986</t>
+          <t>385627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>552865</t>
+          <t>555448</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646236</t>
+          <t>647897</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>789920</t>
+          <t>791115</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>898693</t>
+          <t>894661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1376248</t>
+          <t>1377849</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1510783</t>
+          <t>1515451</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2552237</t>
+          <t>2552675</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2652505</t>
+          <t>2658807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2468587</t>
+          <t>2467351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2581803</t>
+          <t>2578401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5053561</t>
+          <t>5045986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5198847</t>
+          <t>5198786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22417</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15619</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32652</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107158</t>
+          <t>106261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147698</t>
+          <t>147126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185858</t>
+          <t>185724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221940</t>
+          <t>221363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303952</t>
+          <t>301220</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359511</t>
+          <t>356858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>463886</t>
+          <t>464252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505771</t>
+          <t>506189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>420030</t>
+          <t>420478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>456038</t>
+          <t>457747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>895696</t>
+          <t>898311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952150</t>
+          <t>956124</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37965</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92780</t>
+          <t>82996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245886</t>
+          <t>244461</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207717</t>
+          <t>207923</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251384</t>
+          <t>251313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>284491</t>
+          <t>276359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>482016</t>
+          <t>485549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>903748</t>
+          <t>904680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1066273</t>
+          <t>1074856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>652172</t>
+          <t>652118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>696426</t>
+          <t>697130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1567387</t>
+          <t>1567177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1781815</t>
+          <t>1789983</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>48375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140284</t>
+          <t>140019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188624</t>
+          <t>189057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221881</t>
+          <t>224417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>660893</t>
+          <t>608765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387588</t>
+          <t>385501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>907774</t>
+          <t>916740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>441932</t>
+          <t>441860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492580</t>
+          <t>490489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221537</t>
+          <t>273342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645226</t>
+          <t>642225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>608575</t>
+          <t>597524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1111921</t>
+          <t>1115040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>42254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31539</t>
+          <t>32433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54960</t>
+          <t>54821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223305</t>
+          <t>222318</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281687</t>
+          <t>281368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>243375</t>
+          <t>254604</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>342926</t>
+          <t>341932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494472</t>
+          <t>490660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604590</t>
+          <t>602881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>633173</t>
+          <t>633992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>690765</t>
+          <t>692780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>713118</t>
+          <t>713971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>820177</t>
+          <t>812004</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1367407</t>
+          <t>1367775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1481878</t>
+          <t>1486057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33010</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65634</t>
+          <t>64415</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101429</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,47 +10143,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>127251</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>106684</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>150559</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>127251</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>106860</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>150318</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>555872</t>
+          <t>555649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>804671</t>
+          <t>814346</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>957287</t>
+          <t>964315</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1572170</t>
+          <t>1607245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1651941</t>
+          <t>1636959</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2309525</t>
+          <t>2357000</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2503236</t>
+          <t>2493003</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2771638</t>
+          <t>2764034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1916101</t>
+          <t>1893941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2514675</t>
+          <t>2510660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4492493</t>
+          <t>4450941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5138820</t>
+          <t>5157772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>29651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30757</t>
+          <t>29467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56755</t>
+          <t>56164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88923</t>
+          <t>87968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93456</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132326</t>
+          <t>130673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160133</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208657</t>
+          <t>208226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>571241</t>
+          <t>573345</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>607511</t>
+          <t>608861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>533258</t>
+          <t>533961</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>575390</t>
+          <t>574603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1116085</t>
+          <t>1119681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1172147</t>
+          <t>1172812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>47844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45609</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74799</t>
+          <t>77086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116848</t>
+          <t>115192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113213</t>
+          <t>112223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>158929</t>
+          <t>159449</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>173753</t>
+          <t>175604</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225587</t>
+          <t>228943</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>301775</t>
+          <t>304232</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>373206</t>
+          <t>367654</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>726930</t>
+          <t>725902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>778976</t>
+          <t>779770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>701946</t>
+          <t>701189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>757605</t>
+          <t>756296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1439701</t>
+          <t>1443766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1518491</t>
+          <t>1515709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>34888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66861</t>
+          <t>66771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92301</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131057</t>
+          <t>130660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>156499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200021</t>
+          <t>202165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259759</t>
+          <t>261156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318390</t>
+          <t>318984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>512903</t>
+          <t>515003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556284</t>
+          <t>556950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448351</t>
+          <t>446575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496263</t>
+          <t>494404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>978458</t>
+          <t>975837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1040524</t>
+          <t>1038432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>22084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43761</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>40653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69388</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68841</t>
+          <t>68808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>105142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119933</t>
+          <t>119883</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164640</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163768</t>
+          <t>162890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215396</t>
+          <t>212603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295537</t>
+          <t>297962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359898</t>
+          <t>368863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>725693</t>
+          <t>727418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>773764</t>
+          <t>773546</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>763987</t>
+          <t>762173</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>818790</t>
+          <t>817598</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1508754</t>
+          <t>1505939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1578864</t>
+          <t>1577937</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117421</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108510</t>
+          <t>109096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153480</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>241568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>305462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>419514</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>500762</t>
+          <t>503270</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>630708</t>
+          <t>633559</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>722399</t>
+          <t>730030</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1073329</t>
+          <t>1075370</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1192458</t>
+          <t>1196163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>26630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51859</t>
+          <t>51574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39573</t>
+          <t>42402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>51636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>82507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135281</t>
+          <t>136662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179710</t>
+          <t>177576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226508</t>
+          <t>226875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>327858</t>
+          <t>326556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>396628</t>
+          <t>393139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>481461</t>
+          <t>484066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>529482</t>
+          <t>530111</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>441247</t>
+          <t>440892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>490721</t>
+          <t>491970</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>934431</t>
+          <t>937167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1006297</t>
+          <t>1006040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,95%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49291</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81153</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>53297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85327</t>
+          <t>87571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110670</t>
+          <t>109812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>158913</t>
+          <t>157118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>178220</t>
+          <t>177696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230213</t>
+          <t>234674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>251767</t>
+          <t>253164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>311824</t>
+          <t>312976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>448977</t>
+          <t>448024</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>529155</t>
+          <t>528857</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>719667</t>
+          <t>719253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>775604</t>
+          <t>778751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>649722</t>
+          <t>647142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>712514</t>
+          <t>711078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1380295</t>
+          <t>1379132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1469136</t>
+          <t>1468512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>51320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88486</t>
+          <t>84188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>115089</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160762</t>
+          <t>163179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169592</t>
+          <t>173605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218856</t>
+          <t>221075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>298831</t>
+          <t>299065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366571</t>
+          <t>366431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>557764</t>
+          <t>559556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608382</t>
+          <t>610516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522266</t>
+          <t>520901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573827</t>
+          <t>573207</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1097831</t>
+          <t>1097092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168645</t>
+          <t>1169431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43648</t>
+          <t>44930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74156</t>
+          <t>76103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66341</t>
+          <t>66433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>88589</t>
+          <t>88609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129398</t>
+          <t>132012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168339</t>
+          <t>170306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>223185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>260329</t>
+          <t>264392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319247</t>
+          <t>318476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446227</t>
+          <t>448759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>523967</t>
+          <t>521240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>657622</t>
+          <t>658558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>713454</t>
+          <t>715256</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>672749</t>
+          <t>672767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>733412</t>
+          <t>729990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1348374</t>
+          <t>1348933</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1432030</t>
+          <t>1430068</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>166389</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224016</t>
+          <t>224661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154515</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208287</t>
+          <t>208155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335840</t>
+          <t>337104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412757</t>
+          <t>415049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642439</t>
+          <t>645494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>740652</t>
+          <t>743904</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>915501</t>
+          <t>921748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1034270</t>
+          <t>1030795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1588104</t>
+          <t>1595423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1742073</t>
+          <t>1739112</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2471615</t>
+          <t>2478624</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2581173</t>
+          <t>2587028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2329295</t>
+          <t>2332575</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2449801</t>
+          <t>2454347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4851463</t>
+          <t>4842440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5009745</t>
+          <t>4994265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56976</t>
+          <t>57472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59287</t>
+          <t>58339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70674</t>
+          <t>69695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105578</t>
+          <t>104709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>81866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120929</t>
+          <t>118610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140095</t>
+          <t>141839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184955</t>
+          <t>182889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232246</t>
+          <t>234954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293227</t>
+          <t>292004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>507067</t>
+          <t>506189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>550679</t>
+          <t>549304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>433208</t>
+          <t>436242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481863</t>
+          <t>482128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952749</t>
+          <t>955100</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1017561</t>
+          <t>1018992</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43166</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48358</t>
+          <t>48681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>47650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>81568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144657</t>
+          <t>145323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193657</t>
+          <t>194035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221870</t>
+          <t>220922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277847</t>
+          <t>277458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>376935</t>
+          <t>383463</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>453075</t>
+          <t>460179</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>792646</t>
+          <t>794264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>845302</t>
+          <t>846173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>725997</t>
+          <t>726984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>786637</t>
+          <t>787144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1537052</t>
+          <t>1533950</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1615510</t>
+          <t>1615246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36259</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63984</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>50176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>67238</t>
+          <t>67614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>103632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129290</t>
+          <t>129961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174192</t>
+          <t>174067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180552</t>
+          <t>180791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230616</t>
+          <t>233317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320819</t>
+          <t>321767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386975</t>
+          <t>392019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>534531</t>
+          <t>534420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585550</t>
+          <t>584901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517904</t>
+          <t>512983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569613</t>
+          <t>570315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1068561</t>
+          <t>1065337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1140714</t>
+          <t>1139734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49522</t>
+          <t>49502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78672</t>
+          <t>79521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64593</t>
+          <t>65311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91586</t>
+          <t>93049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133578</t>
+          <t>131884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161098</t>
+          <t>160908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211256</t>
+          <t>213181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202082</t>
+          <t>198845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>256233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>379327</t>
+          <t>375519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>448967</t>
+          <t>451455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>662974</t>
+          <t>659921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>716948</t>
+          <t>716424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>731606</t>
+          <t>732636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>791465</t>
+          <t>792832</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1414247</t>
+          <t>1414249</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1491979</t>
+          <t>1496804</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159493</t>
+          <t>157241</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214797</t>
+          <t>210958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136422</t>
+          <t>137599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188581</t>
+          <t>190064</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>309390</t>
+          <t>309018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385627</t>
+          <t>384101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>555448</t>
+          <t>555093</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>647897</t>
+          <t>645022</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>791115</t>
+          <t>793807</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>894661</t>
+          <t>896236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1377849</t>
+          <t>1374091</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1515451</t>
+          <t>1519763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2552675</t>
+          <t>2549311</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2658807</t>
+          <t>2652481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2467351</t>
+          <t>2467735</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2578401</t>
+          <t>2577470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5045986</t>
+          <t>5046798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5198786</t>
+          <t>5201128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>23208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15810</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125752</t>
+          <t>141384</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106261</t>
+          <t>119696</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147126</t>
+          <t>163996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>203855</t>
+          <t>218460</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185724</t>
+          <t>200576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>221363</t>
+          <t>237687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>329607</t>
+          <t>359843</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301220</t>
+          <t>329905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356858</t>
+          <t>389507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>486818</t>
+          <t>524808</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>464252</t>
+          <t>499783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>506189</t>
+          <t>545685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>439024</t>
+          <t>480474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>420478</t>
+          <t>460904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>457747</t>
+          <t>498987</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>925842</t>
+          <t>1005283</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>898311</t>
+          <t>973362</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>956124</t>
+          <t>1034562</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>622044</t>
+          <t>676336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>656603</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1278647</t>
+          <t>1389218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>23197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>34492</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>25429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>48241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>186444</t>
+          <t>195723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82996</t>
+          <t>168833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>244461</t>
+          <t>220285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>229803</t>
+          <t>250204</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207923</t>
+          <t>228590</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251313</t>
+          <t>274249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>416247</t>
+          <t>445927</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>276359</t>
+          <t>410723</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>485549</t>
+          <t>481672</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>965770</t>
+          <t>811792</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>904680</t>
+          <t>784923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1074856</t>
+          <t>839618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>673534</t>
+          <t>758917</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>652118</t>
+          <t>732972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>697130</t>
+          <t>780245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1639304</t>
+          <t>1570709</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1567177</t>
+          <t>1535995</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1789983</t>
+          <t>1607558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1162903</t>
+          <t>1021564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>919321</t>
+          <t>1029564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2082224</t>
+          <t>2051128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22070</t>
+          <t>25009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48375</t>
+          <t>52050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>164945</t>
+          <t>185547</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140019</t>
+          <t>159238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189057</t>
+          <t>212254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>385872</t>
+          <t>209835</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224417</t>
+          <t>186499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>608765</t>
+          <t>230758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>550818</t>
+          <t>395383</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385501</t>
+          <t>361268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>916740</t>
+          <t>429072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>466464</t>
+          <t>539227</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>441860</t>
+          <t>512152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490489</t>
+          <t>565852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>535189</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273342</t>
+          <t>513510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642225</t>
+          <t>558355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>953384</t>
+          <t>1074417</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>597524</t>
+          <t>1039316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1115040</t>
+          <t>1114011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646101</t>
+          <t>741446</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>893360</t>
+          <t>767981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1539461</t>
+          <t>1509427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>31330</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>26426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42254</t>
+          <t>48228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42121</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>59602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>251916</t>
+          <t>265727</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>222318</t>
+          <t>238636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281368</t>
+          <t>297480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>309858</t>
+          <t>341616</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>254604</t>
+          <t>314598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341932</t>
+          <t>369556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>561774</t>
+          <t>607342</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490660</t>
+          <t>569981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>602881</t>
+          <t>648324</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>663126</t>
+          <t>712410</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>633992</t>
+          <t>681417</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>692780</t>
+          <t>740390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747977</t>
+          <t>735948</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>713971</t>
+          <t>705542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>812004</t>
+          <t>761771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1411102</t>
+          <t>1448358</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1367775</t>
+          <t>1408390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1486057</t>
+          <t>1488439</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1089165</t>
+          <t>1113176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2014997</t>
+          <t>2102314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45644</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32721</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60908</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>92960</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>77934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98202</t>
+          <t>111150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>127251</t>
+          <t>144825</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106684</t>
+          <t>123783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150559</t>
+          <t>166951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>729058</t>
+          <t>788381</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>555649</t>
+          <t>734107</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>814346</t>
+          <t>840252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1129388</t>
+          <t>1020114</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>964315</t>
+          <t>973659</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1607245</t>
+          <t>1068097</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1858446</t>
+          <t>1808495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1636959</t>
+          <t>1735921</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2357000</t>
+          <t>1876718</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2582177</t>
+          <t>2588239</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2493003</t>
+          <t>2534456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2764034</t>
+          <t>2641203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2347455</t>
+          <t>2510528</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1893941</t>
+          <t>2453912</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2510660</t>
+          <t>2557005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4929632</t>
+          <t>5098767</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4450941</t>
+          <t>5028185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5157772</t>
+          <t>5172690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3356879</t>
+          <t>3428485</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3558450</t>
+          <t>3623602</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6915329</t>
+          <t>7052087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
